--- a/projects/NZIPL/docs/trade_data/latest_2024/NZIPL_2024_RoleStage_Imports_USDmn.xlsx
+++ b/projects/NZIPL/docs/trade_data/latest_2024/NZIPL_2024_RoleStage_Imports_USDmn.xlsx
@@ -94,7 +94,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-10</t>
+    <t xml:space="preserve">2026-07-11</t>
   </si>
   <si>
     <t xml:space="preserve">ISO3</t>
@@ -7692,7 +7692,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.979</v>
+        <v>7.957</v>
       </c>
     </row>
     <row r="9">
@@ -7811,7 +7811,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>187.157</v>
+        <v>374.315</v>
       </c>
     </row>
     <row r="16">
@@ -7930,7 +7930,7 @@
         <v>38</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>93.796</v>
+        <v>187.591</v>
       </c>
     </row>
     <row r="23">
@@ -8049,7 +8049,7 @@
         <v>38</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>189.551</v>
+        <v>379.103</v>
       </c>
     </row>
     <row r="30">
@@ -8168,7 +8168,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>65.794</v>
+        <v>131.588</v>
       </c>
     </row>
     <row r="37">
@@ -8287,7 +8287,7 @@
         <v>38</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>133.306</v>
+        <v>266.613</v>
       </c>
     </row>
     <row r="44">
@@ -8406,7 +8406,7 @@
         <v>38</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>38.798</v>
+        <v>77.596</v>
       </c>
     </row>
     <row r="51">
@@ -8525,7 +8525,7 @@
         <v>38</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>61.732</v>
+        <v>123.464</v>
       </c>
     </row>
     <row r="58">
@@ -8644,7 +8644,7 @@
         <v>38</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>7.785</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="65">
@@ -8763,7 +8763,7 @@
         <v>38</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>319.415</v>
+        <v>638.831</v>
       </c>
     </row>
     <row r="72">
@@ -8882,7 +8882,7 @@
         <v>38</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>8.321</v>
+        <v>16.643</v>
       </c>
     </row>
     <row r="79">
@@ -9001,7 +9001,7 @@
         <v>38</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>144.368</v>
+        <v>288.736</v>
       </c>
     </row>
     <row r="86">
@@ -9120,7 +9120,7 @@
         <v>38</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>14.882</v>
+        <v>29.764</v>
       </c>
     </row>
     <row r="93">
@@ -9239,7 +9239,7 @@
         <v>38</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>65.996</v>
+        <v>131.992</v>
       </c>
     </row>
     <row r="100">
@@ -9358,7 +9358,7 @@
         <v>38</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>5.458</v>
+        <v>10.916</v>
       </c>
     </row>
     <row r="107">
@@ -9477,7 +9477,7 @@
         <v>38</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>180.353</v>
+        <v>360.707</v>
       </c>
     </row>
     <row r="114">
@@ -9596,7 +9596,7 @@
         <v>38</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>171.003</v>
+        <v>342.006</v>
       </c>
     </row>
     <row r="121">
@@ -9715,7 +9715,7 @@
         <v>38</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>0.101</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="128">
@@ -9834,7 +9834,7 @@
         <v>38</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>46.461</v>
+        <v>92.922</v>
       </c>
     </row>
     <row r="135">
@@ -9953,7 +9953,7 @@
         <v>38</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>198.113</v>
+        <v>396.225</v>
       </c>
     </row>
     <row r="142">
@@ -10072,7 +10072,7 @@
         <v>38</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>1.053</v>
+        <v>2.107</v>
       </c>
     </row>
     <row r="149">
@@ -10191,15 +10191,15 @@
         <v>38</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>10.747</v>
+        <v>21.495</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B156" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C156" t="s">
         <v>31</v>
@@ -10208,15 +10208,15 @@
         <v>32</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>350.285</v>
+        <v>1482.682</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B157" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C157" t="s">
         <v>33</v>
@@ -10225,15 +10225,15 @@
         <v>34</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>7.896</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B158" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C158" t="s">
         <v>33</v>
@@ -10242,15 +10242,15 @@
         <v>35</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>2234.975</v>
+        <v>1238.508</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B159" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C159" t="s">
         <v>33</v>
@@ -10259,15 +10259,15 @@
         <v>36</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>6423.513</v>
+        <v>3484.132</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B160" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C160" t="s">
         <v>37</v>
@@ -10276,15 +10276,15 @@
         <v>34</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>515.664</v>
+        <v>300.065</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B161" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C161" t="s">
         <v>37</v>
@@ -10293,15 +10293,15 @@
         <v>36</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>947.168</v>
+        <v>1459.316</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B162" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C162" t="s">
         <v>38</v>
@@ -10310,15 +10310,15 @@
         <v>38</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>0</v>
+        <v>132.502</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B163" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C163" t="s">
         <v>31</v>
@@ -10327,15 +10327,15 @@
         <v>32</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>1482.682</v>
+        <v>350.285</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B164" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C164" t="s">
         <v>33</v>
@@ -10344,15 +10344,15 @@
         <v>34</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>17.01</v>
+        <v>7.896</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B165" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C165" t="s">
         <v>33</v>
@@ -10361,15 +10361,15 @@
         <v>35</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>1238.508</v>
+        <v>2234.975</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B166" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C166" t="s">
         <v>33</v>
@@ -10378,15 +10378,15 @@
         <v>36</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>3484.132</v>
+        <v>6423.513</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B167" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C167" t="s">
         <v>37</v>
@@ -10395,15 +10395,15 @@
         <v>34</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>300.065</v>
+        <v>515.664</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B168" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C168" t="s">
         <v>37</v>
@@ -10412,15 +10412,15 @@
         <v>36</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>1459.316</v>
+        <v>947.168</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B169" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C169" t="s">
         <v>38</v>
@@ -10429,7 +10429,7 @@
         <v>38</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>66.251</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -10548,7 +10548,7 @@
         <v>38</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>260.581</v>
+        <v>521.162</v>
       </c>
     </row>
     <row r="177">
@@ -10667,7 +10667,7 @@
         <v>38</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>1.114</v>
+        <v>2.228</v>
       </c>
     </row>
     <row r="184">
@@ -10888,7 +10888,7 @@
         <v>38</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>0.19</v>
+        <v>0.381</v>
       </c>
     </row>
     <row r="197">
@@ -11007,7 +11007,7 @@
         <v>38</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>0.074</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="204">
@@ -11126,7 +11126,7 @@
         <v>38</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>0.203</v>
+        <v>0.406</v>
       </c>
     </row>
   </sheetData>
@@ -11280,7 +11280,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>978.109</v>
+        <v>984.268</v>
       </c>
     </row>
     <row r="9">
@@ -11399,7 +11399,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1686.824</v>
+        <v>1693.457</v>
       </c>
     </row>
     <row r="16">
@@ -11518,7 +11518,7 @@
         <v>38</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>11480.545</v>
+        <v>11514.215</v>
       </c>
     </row>
     <row r="23">
@@ -11637,7 +11637,7 @@
         <v>38</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>12694.994</v>
+        <v>12738.802</v>
       </c>
     </row>
     <row r="30">
@@ -11756,7 +11756,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1355.615</v>
+        <v>1358.542</v>
       </c>
     </row>
     <row r="37">
@@ -11875,7 +11875,7 @@
         <v>38</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2386.231</v>
+        <v>2395.47</v>
       </c>
     </row>
     <row r="44">
@@ -11994,7 +11994,7 @@
         <v>38</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>339.831</v>
+        <v>344.96</v>
       </c>
     </row>
     <row r="51">
@@ -12113,7 +12113,7 @@
         <v>38</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>1095.945</v>
+        <v>1119.922</v>
       </c>
     </row>
     <row r="58">
@@ -12232,7 +12232,7 @@
         <v>38</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>977.531</v>
+        <v>995.007</v>
       </c>
     </row>
     <row r="65">
@@ -12351,7 +12351,7 @@
         <v>38</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>1783.78</v>
+        <v>1798.401</v>
       </c>
     </row>
     <row r="72">
@@ -12470,7 +12470,7 @@
         <v>38</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>1479.7</v>
+        <v>1486.651</v>
       </c>
     </row>
     <row r="79">
@@ -12589,7 +12589,7 @@
         <v>38</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>1366.819</v>
+        <v>1379.208</v>
       </c>
     </row>
     <row r="86">
@@ -12708,7 +12708,7 @@
         <v>38</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>284.413</v>
+        <v>528.748</v>
       </c>
     </row>
     <row r="93">
@@ -12827,7 +12827,7 @@
         <v>38</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1417.94</v>
+        <v>1423.034</v>
       </c>
     </row>
     <row r="100">
@@ -12946,7 +12946,7 @@
         <v>38</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>636.181</v>
+        <v>649.759</v>
       </c>
     </row>
     <row r="107">
@@ -13065,7 +13065,7 @@
         <v>38</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>823.582</v>
+        <v>829.746</v>
       </c>
     </row>
     <row r="114">
@@ -13184,7 +13184,7 @@
         <v>38</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>2792.926</v>
+        <v>2801.117</v>
       </c>
     </row>
     <row r="121">
@@ -13303,7 +13303,7 @@
         <v>38</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>218.478</v>
+        <v>222.097</v>
       </c>
     </row>
     <row r="128">
@@ -13422,7 +13422,7 @@
         <v>38</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>936.777</v>
+        <v>953.621</v>
       </c>
     </row>
     <row r="135">
@@ -13541,7 +13541,7 @@
         <v>38</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>179.992</v>
+        <v>180.387</v>
       </c>
     </row>
     <row r="142">
@@ -13660,7 +13660,7 @@
         <v>38</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>245.748</v>
+        <v>253.756</v>
       </c>
     </row>
     <row r="149">
@@ -13779,7 +13779,7 @@
         <v>38</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>231.284</v>
+        <v>246.939</v>
       </c>
     </row>
     <row r="156">
@@ -13898,7 +13898,7 @@
         <v>38</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>27.812</v>
+        <v>30.044</v>
       </c>
     </row>
     <row r="163">
@@ -14017,7 +14017,7 @@
         <v>38</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>855.795</v>
+        <v>876.4</v>
       </c>
     </row>
     <row r="170">
@@ -14136,7 +14136,7 @@
         <v>38</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>196.603</v>
+        <v>201.517</v>
       </c>
     </row>
     <row r="177">
@@ -14255,7 +14255,7 @@
         <v>38</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>209.297</v>
+        <v>214.57</v>
       </c>
     </row>
     <row r="184">
@@ -14374,7 +14374,7 @@
         <v>38</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>1038.268</v>
+        <v>1043.832</v>
       </c>
     </row>
     <row r="191">
@@ -14493,7 +14493,7 @@
         <v>38</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>898.655</v>
+        <v>905.266</v>
       </c>
     </row>
     <row r="198">
@@ -14612,7 +14612,7 @@
         <v>38</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>559.4</v>
+        <v>563.239</v>
       </c>
     </row>
     <row r="205">
@@ -14731,7 +14731,7 @@
         <v>38</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>616.8</v>
+        <v>618.661</v>
       </c>
     </row>
   </sheetData>
@@ -14851,7 +14851,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>960.077</v>
+        <v>1851.885</v>
       </c>
     </row>
     <row r="7">
@@ -14936,7 +14936,7 @@
         <v>38</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1239.531</v>
+        <v>2328.908</v>
       </c>
     </row>
     <row r="12">
@@ -15021,7 +15021,7 @@
         <v>38</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>13.516</v>
+        <v>25.758</v>
       </c>
     </row>
     <row r="17">
@@ -15106,7 +15106,7 @@
         <v>38</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.664</v>
+        <v>0.936</v>
       </c>
     </row>
     <row r="22">
@@ -15191,7 +15191,7 @@
         <v>38</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>620.01</v>
+        <v>1073.969</v>
       </c>
     </row>
     <row r="27">
@@ -15276,7 +15276,7 @@
         <v>38</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2858.515</v>
+        <v>5517.912</v>
       </c>
     </row>
     <row r="32">
@@ -15361,7 +15361,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>508.059</v>
+        <v>985.39</v>
       </c>
     </row>
     <row r="37">
@@ -15446,7 +15446,7 @@
         <v>38</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>154.721</v>
+        <v>164.828</v>
       </c>
     </row>
     <row r="42">
@@ -15531,15 +15531,15 @@
         <v>38</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1271.327</v>
+        <v>2513.347</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
         <v>31</v>
@@ -15548,15 +15548,15 @@
         <v>32</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>80.201</v>
+        <v>615.393</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C48" t="s">
         <v>33</v>
@@ -15565,15 +15565,15 @@
         <v>34</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>19.181</v>
+        <v>269.419</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
         <v>33</v>
@@ -15582,15 +15582,15 @@
         <v>35</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>1241.719</v>
+        <v>3328.526</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
         <v>37</v>
@@ -15599,15 +15599,15 @@
         <v>34</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>364.63</v>
+        <v>1093.082</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s">
         <v>38</v>
@@ -15616,15 +15616,15 @@
         <v>38</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>1.109</v>
+        <v>2902.025</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C52" t="s">
         <v>31</v>
@@ -15633,15 +15633,15 @@
         <v>32</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>615.393</v>
+        <v>80.201</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C53" t="s">
         <v>33</v>
@@ -15650,15 +15650,15 @@
         <v>34</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>269.419</v>
+        <v>19.181</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B54" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C54" t="s">
         <v>33</v>
@@ -15667,15 +15667,15 @@
         <v>35</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>3328.526</v>
+        <v>1241.719</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C55" t="s">
         <v>37</v>
@@ -15684,15 +15684,15 @@
         <v>34</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1093.082</v>
+        <v>364.63</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C56" t="s">
         <v>38</v>
@@ -15701,7 +15701,7 @@
         <v>38</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1492.464</v>
+        <v>1.109</v>
       </c>
     </row>
     <row r="57">
@@ -15786,7 +15786,7 @@
         <v>38</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>1772.304</v>
+        <v>2163.532</v>
       </c>
     </row>
     <row r="62">
@@ -16041,7 +16041,7 @@
         <v>38</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>485.993</v>
+        <v>861.197</v>
       </c>
     </row>
     <row r="77">
@@ -16126,7 +16126,7 @@
         <v>38</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>123.961</v>
+        <v>243.777</v>
       </c>
     </row>
     <row r="82">
@@ -16211,7 +16211,7 @@
         <v>38</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>31.448</v>
+        <v>31.57</v>
       </c>
     </row>
     <row r="87">
@@ -16296,7 +16296,7 @@
         <v>38</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>0.319</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="92">
@@ -16551,7 +16551,7 @@
         <v>38</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>74.588</v>
+        <v>137.25</v>
       </c>
     </row>
     <row r="107">
@@ -16636,15 +16636,15 @@
         <v>38</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>2.252</v>
+        <v>2.561</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B112" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C112" t="s">
         <v>31</v>
@@ -16653,15 +16653,15 @@
         <v>32</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>153.53</v>
+        <v>148.123</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B113" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C113" t="s">
         <v>33</v>
@@ -16670,15 +16670,15 @@
         <v>34</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>105.251</v>
+        <v>111.736</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B114" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C114" t="s">
         <v>33</v>
@@ -16687,15 +16687,15 @@
         <v>35</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>1265.672</v>
+        <v>1650.532</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B115" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C115" t="s">
         <v>37</v>
@@ -16704,15 +16704,15 @@
         <v>34</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>1123.193</v>
+        <v>1491.129</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B116" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C116" t="s">
         <v>38</v>
@@ -16721,15 +16721,15 @@
         <v>38</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>12.74</v>
+        <v>505.75</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B117" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C117" t="s">
         <v>31</v>
@@ -16738,15 +16738,15 @@
         <v>32</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>148.123</v>
+        <v>153.53</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B118" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C118" t="s">
         <v>33</v>
@@ -16755,15 +16755,15 @@
         <v>34</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>111.736</v>
+        <v>105.251</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B119" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C119" t="s">
         <v>33</v>
@@ -16772,15 +16772,15 @@
         <v>35</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>1650.532</v>
+        <v>1265.672</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B120" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C120" t="s">
         <v>37</v>
@@ -16789,15 +16789,15 @@
         <v>34</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>1491.129</v>
+        <v>1123.193</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C121" t="s">
         <v>38</v>
@@ -16806,7 +16806,7 @@
         <v>38</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>259.12</v>
+        <v>13.913</v>
       </c>
     </row>
     <row r="122">
@@ -16976,7 +16976,7 @@
         <v>38</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>180.499</v>
+        <v>263.699</v>
       </c>
     </row>
     <row r="132">
@@ -17061,7 +17061,7 @@
         <v>38</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>249.855</v>
+        <v>481.493</v>
       </c>
     </row>
     <row r="137">
@@ -17146,7 +17146,7 @@
         <v>38</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>53.743</v>
+        <v>53.867</v>
       </c>
     </row>
     <row r="142">
@@ -17231,7 +17231,7 @@
         <v>38</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>178.205</v>
+        <v>283.563</v>
       </c>
     </row>
     <row r="147">
@@ -17316,7 +17316,7 @@
         <v>38</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>5.59</v>
+        <v>10.988</v>
       </c>
     </row>
   </sheetData>
@@ -17368,7 +17368,7 @@
         <v>32</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>196005.701</v>
+        <v>198950.833</v>
       </c>
     </row>
     <row r="3">
@@ -17572,7 +17572,7 @@
         <v>32</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>4810.505</v>
+        <v>4854.374</v>
       </c>
     </row>
     <row r="15">
@@ -17674,7 +17674,7 @@
         <v>32</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>22538.537</v>
+        <v>22730.138</v>
       </c>
     </row>
     <row r="21">
@@ -17776,7 +17776,7 @@
         <v>32</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>181.241</v>
+        <v>227.297</v>
       </c>
     </row>
     <row r="27">
@@ -17878,7 +17878,7 @@
         <v>32</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2397.032</v>
+        <v>2417.607</v>
       </c>
     </row>
     <row r="33">
@@ -18082,7 +18082,7 @@
         <v>32</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>12948.847</v>
+        <v>13323.587</v>
       </c>
     </row>
     <row r="45">
@@ -18490,7 +18490,7 @@
         <v>32</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>571.055</v>
+        <v>571.285</v>
       </c>
     </row>
     <row r="69">
@@ -18592,7 +18592,7 @@
         <v>32</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>3429.258</v>
+        <v>3450.008</v>
       </c>
     </row>
     <row r="75">
@@ -18694,7 +18694,7 @@
         <v>32</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>3196.066</v>
+        <v>3196.219</v>
       </c>
     </row>
     <row r="81">
@@ -18898,7 +18898,7 @@
         <v>32</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>951.089</v>
+        <v>1089.089</v>
       </c>
     </row>
     <row r="93">
@@ -19408,7 +19408,7 @@
         <v>32</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>990.503</v>
+        <v>1023.367</v>
       </c>
     </row>
     <row r="123">
@@ -19612,7 +19612,7 @@
         <v>32</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>153.94</v>
+        <v>183.525</v>
       </c>
     </row>
     <row r="135">
@@ -19714,7 +19714,7 @@
         <v>32</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>548.891</v>
+        <v>549.133</v>
       </c>
     </row>
     <row r="141">
@@ -19918,7 +19918,7 @@
         <v>32</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>2344.288</v>
+        <v>2344.403</v>
       </c>
     </row>
     <row r="153">
@@ -20020,7 +20020,7 @@
         <v>32</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>2686.198</v>
+        <v>2686.544</v>
       </c>
     </row>
     <row r="159">
@@ -20224,7 +20224,7 @@
         <v>32</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>27.046</v>
+        <v>29.636</v>
       </c>
     </row>
     <row r="171">
@@ -20326,7 +20326,7 @@
         <v>32</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>435.304</v>
+        <v>436.376</v>
       </c>
     </row>
     <row r="177">
@@ -20565,7 +20565,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>92.112</v>
+        <v>184.224</v>
       </c>
     </row>
     <row r="9">
@@ -20684,7 +20684,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>85.426</v>
+        <v>170.853</v>
       </c>
     </row>
     <row r="16">
@@ -20803,7 +20803,7 @@
         <v>38</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>26.557</v>
+        <v>53.114</v>
       </c>
     </row>
     <row r="23">
@@ -20922,7 +20922,7 @@
         <v>38</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>16.342</v>
+        <v>32.684</v>
       </c>
     </row>
     <row r="30">
@@ -21041,7 +21041,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>24.077</v>
+        <v>48.154</v>
       </c>
     </row>
     <row r="37">
@@ -21160,7 +21160,7 @@
         <v>38</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>7.329</v>
+        <v>14.659</v>
       </c>
     </row>
     <row r="44">
@@ -21279,7 +21279,7 @@
         <v>38</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>17.048</v>
+        <v>34.096</v>
       </c>
     </row>
     <row r="51">
@@ -21398,7 +21398,7 @@
         <v>38</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>46.682</v>
+        <v>93.364</v>
       </c>
     </row>
     <row r="58">
@@ -21517,7 +21517,7 @@
         <v>38</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>18.612</v>
+        <v>37.224</v>
       </c>
     </row>
     <row r="65">
@@ -21636,7 +21636,7 @@
         <v>38</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>12.762</v>
+        <v>25.524</v>
       </c>
     </row>
     <row r="72">
@@ -21755,7 +21755,7 @@
         <v>38</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>4.996</v>
+        <v>9.992</v>
       </c>
     </row>
     <row r="79">
@@ -21874,7 +21874,7 @@
         <v>38</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>12.071</v>
+        <v>24.143</v>
       </c>
     </row>
     <row r="86">
@@ -21993,7 +21993,7 @@
         <v>38</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>59.677</v>
+        <v>119.354</v>
       </c>
     </row>
     <row r="93">
@@ -22112,7 +22112,7 @@
         <v>38</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>9.664</v>
+        <v>19.328</v>
       </c>
     </row>
     <row r="100">
@@ -22231,7 +22231,7 @@
         <v>38</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>1.69</v>
+        <v>3.381</v>
       </c>
     </row>
     <row r="107">
@@ -22350,7 +22350,7 @@
         <v>38</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>5.251</v>
+        <v>10.503</v>
       </c>
     </row>
     <row r="114">
@@ -22469,7 +22469,7 @@
         <v>38</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>16.254</v>
+        <v>32.508</v>
       </c>
     </row>
     <row r="121">
@@ -22588,7 +22588,7 @@
         <v>38</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>5.513</v>
+        <v>11.025</v>
       </c>
     </row>
     <row r="128">
@@ -22707,7 +22707,7 @@
         <v>38</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>7.252</v>
+        <v>14.504</v>
       </c>
     </row>
     <row r="135">
@@ -22826,7 +22826,7 @@
         <v>38</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>50.677</v>
+        <v>101.354</v>
       </c>
     </row>
     <row r="142">
@@ -22945,7 +22945,7 @@
         <v>38</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>12.774</v>
+        <v>25.549</v>
       </c>
     </row>
     <row r="149">
@@ -23064,7 +23064,7 @@
         <v>38</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>24.45</v>
+        <v>48.901</v>
       </c>
     </row>
     <row r="156">
@@ -23183,7 +23183,7 @@
         <v>38</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>30.317</v>
+        <v>60.634</v>
       </c>
     </row>
     <row r="163">
@@ -23302,7 +23302,7 @@
         <v>38</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>0.829</v>
+        <v>1.658</v>
       </c>
     </row>
     <row r="170">
@@ -23421,7 +23421,7 @@
         <v>38</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>2.44</v>
+        <v>4.879</v>
       </c>
     </row>
     <row r="177">
@@ -23540,7 +23540,7 @@
         <v>38</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>8.609</v>
+        <v>17.218</v>
       </c>
     </row>
     <row r="184">
@@ -23659,7 +23659,7 @@
         <v>38</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>41.576</v>
+        <v>83.151</v>
       </c>
     </row>
     <row r="191">
@@ -23778,7 +23778,7 @@
         <v>38</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>15.595</v>
+        <v>31.19</v>
       </c>
     </row>
     <row r="198">
@@ -23897,7 +23897,7 @@
         <v>38</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>40.892</v>
+        <v>81.783</v>
       </c>
     </row>
     <row r="205">
@@ -24016,7 +24016,7 @@
         <v>38</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>18.11</v>
+        <v>36.22</v>
       </c>
     </row>
   </sheetData>
@@ -31346,7 +31346,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>123.437</v>
+        <v>188.205</v>
       </c>
     </row>
     <row r="7">
@@ -31431,7 +31431,7 @@
         <v>38</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>319.635</v>
+        <v>603.937</v>
       </c>
     </row>
     <row r="12">
@@ -31516,7 +31516,7 @@
         <v>38</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>308.598</v>
+        <v>554.161</v>
       </c>
     </row>
     <row r="17">
@@ -31601,7 +31601,7 @@
         <v>38</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>398.891</v>
+        <v>708.211</v>
       </c>
     </row>
     <row r="22">
@@ -31686,7 +31686,7 @@
         <v>38</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1.633</v>
+        <v>2.815</v>
       </c>
     </row>
     <row r="27">
@@ -31771,7 +31771,7 @@
         <v>38</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>182.345</v>
+        <v>335.52</v>
       </c>
     </row>
     <row r="32">
@@ -31856,7 +31856,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>44.002</v>
+        <v>63.57</v>
       </c>
     </row>
     <row r="37">
@@ -31941,7 +31941,7 @@
         <v>38</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.988</v>
+        <v>1.486</v>
       </c>
     </row>
     <row r="42">
@@ -32026,7 +32026,7 @@
         <v>38</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>15.522</v>
+        <v>23.073</v>
       </c>
     </row>
     <row r="47">
@@ -32111,7 +32111,7 @@
         <v>38</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>79.553</v>
+        <v>125.643</v>
       </c>
     </row>
     <row r="52">
@@ -32196,7 +32196,7 @@
         <v>38</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>26.676</v>
+        <v>37.081</v>
       </c>
     </row>
     <row r="57">
@@ -32281,7 +32281,7 @@
         <v>38</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>21.736</v>
+        <v>32.454</v>
       </c>
     </row>
     <row r="62">
@@ -32366,7 +32366,7 @@
         <v>38</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>32.79</v>
+        <v>51.832</v>
       </c>
     </row>
     <row r="67">
@@ -32451,7 +32451,7 @@
         <v>38</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>133.091</v>
+        <v>230.236</v>
       </c>
     </row>
     <row r="72">
@@ -32536,7 +32536,7 @@
         <v>38</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>170.843</v>
+        <v>293.207</v>
       </c>
     </row>
     <row r="77">
@@ -32621,7 +32621,7 @@
         <v>38</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>53.201</v>
+        <v>94.497</v>
       </c>
     </row>
     <row r="82">
@@ -32706,7 +32706,7 @@
         <v>38</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>42.845</v>
+        <v>78.321</v>
       </c>
     </row>
     <row r="87">
@@ -32791,7 +32791,7 @@
         <v>38</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>97.028</v>
+        <v>168.482</v>
       </c>
     </row>
     <row r="92">
@@ -32876,7 +32876,7 @@
         <v>38</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>4.018</v>
+        <v>6.462</v>
       </c>
     </row>
     <row r="97">
@@ -32961,7 +32961,7 @@
         <v>38</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>24.962</v>
+        <v>45.896</v>
       </c>
     </row>
     <row r="102">
@@ -33046,15 +33046,15 @@
         <v>38</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>35.72</v>
+        <v>57.329</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B107" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C107" t="s">
         <v>31</v>
@@ -33063,15 +33063,15 @@
         <v>32</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>23.125</v>
+        <v>1855.7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B108" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C108" t="s">
         <v>33</v>
@@ -33080,15 +33080,15 @@
         <v>35</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>54.824</v>
+        <v>135.375</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B109" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C109" t="s">
         <v>37</v>
@@ -33097,15 +33097,15 @@
         <v>34</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>621.148</v>
+        <v>220.059</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C110" t="s">
         <v>37</v>
@@ -33114,15 +33114,15 @@
         <v>36</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>1.45</v>
+        <v>30.659</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C111" t="s">
         <v>38</v>
@@ -33131,15 +33131,15 @@
         <v>38</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>6.218</v>
+        <v>328.643</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C112" t="s">
         <v>31</v>
@@ -33148,15 +33148,15 @@
         <v>32</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>1855.7</v>
+        <v>23.125</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C113" t="s">
         <v>33</v>
@@ -33165,15 +33165,15 @@
         <v>35</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>135.375</v>
+        <v>54.824</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B114" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C114" t="s">
         <v>37</v>
@@ -33182,15 +33182,15 @@
         <v>34</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>220.059</v>
+        <v>621.148</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B115" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C115" t="s">
         <v>37</v>
@@ -33199,15 +33199,15 @@
         <v>36</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>30.659</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B116" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C116" t="s">
         <v>38</v>
@@ -33216,7 +33216,7 @@
         <v>38</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>179.651</v>
+        <v>10.986</v>
       </c>
     </row>
     <row r="117">
@@ -33301,7 +33301,7 @@
         <v>38</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>76.026</v>
+        <v>135.533</v>
       </c>
     </row>
     <row r="122">
@@ -33386,7 +33386,7 @@
         <v>38</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>45.968</v>
+        <v>82.438</v>
       </c>
     </row>
     <row r="127">
@@ -33471,15 +33471,15 @@
         <v>38</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>87.817</v>
+        <v>156.018</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B132" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C132" t="s">
         <v>31</v>
@@ -33488,15 +33488,15 @@
         <v>32</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>150.324</v>
+        <v>65.384</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B133" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C133" t="s">
         <v>33</v>
@@ -33505,15 +33505,15 @@
         <v>35</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>236.014</v>
+        <v>816.281</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B134" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C134" t="s">
         <v>37</v>
@@ -33522,15 +33522,15 @@
         <v>34</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>1156.254</v>
+        <v>1124.709</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B135" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C135" t="s">
         <v>37</v>
@@ -33539,15 +33539,15 @@
         <v>36</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>15.4</v>
+        <v>42.06</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B136" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C136" t="s">
         <v>38</v>
@@ -33556,15 +33556,15 @@
         <v>38</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>25.666</v>
+        <v>216.001</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B137" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C137" t="s">
         <v>31</v>
@@ -33573,15 +33573,15 @@
         <v>32</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>65.384</v>
+        <v>150.324</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B138" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C138" t="s">
         <v>33</v>
@@ -33590,15 +33590,15 @@
         <v>35</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>816.281</v>
+        <v>236.014</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B139" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C139" t="s">
         <v>37</v>
@@ -33607,15 +33607,15 @@
         <v>34</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>1124.709</v>
+        <v>1156.254</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B140" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C140" t="s">
         <v>37</v>
@@ -33624,15 +33624,15 @@
         <v>36</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>42.06</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B141" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C141" t="s">
         <v>38</v>
@@ -33641,7 +33641,7 @@
         <v>38</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>129.031</v>
+        <v>35.932</v>
       </c>
     </row>
     <row r="142">
@@ -33726,7 +33726,7 @@
         <v>38</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>21.007</v>
+        <v>34.367</v>
       </c>
     </row>
     <row r="147">
@@ -33811,7 +33811,7 @@
         <v>38</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>9.496</v>
+        <v>16.569</v>
       </c>
     </row>
   </sheetData>
@@ -34084,7 +34084,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.076</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="16">
@@ -34441,7 +34441,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>14.298</v>
+        <v>15.109</v>
       </c>
     </row>
     <row r="37">
@@ -35104,7 +35104,7 @@
         <v>38</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>0.058</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="76">
@@ -35801,7 +35801,7 @@
         <v>38</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>3.994</v>
+        <v>4.137</v>
       </c>
     </row>
     <row r="117">
@@ -36974,7 +36974,7 @@
         <v>38</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>0.122</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="186">
@@ -37093,7 +37093,7 @@
         <v>38</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>73.269</v>
+        <v>141.691</v>
       </c>
     </row>
     <row r="193">
